--- a/.claude/build/research/KPC_Park_Hours_worklist.xlsx
+++ b/.claude/build/research/KPC_Park_Hours_worklist.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KY parks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Hours + fees (40)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Hours only (67)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -539,6 +540,13 @@
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Rules: official pages only (parks.ky.gov, eec.ky.gov, fw.ky.gov, nps.gov, fs.usda.gov, fws.gov, the park's own site). Only what the page says. Not there = leave it empty and write NOT ON PAGE in Status. No new tabs or columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TAB 2 "Hours only": after the first tab is done, do these the same way, but HOURS ONLY (these parks are free, skip the fee). Same Status rule: start at the first row with an empty Status.</t>
         </is>
       </c>
     </row>
@@ -1693,4 +1701,1776 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Park ref</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Park name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Our link</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Hours (YOU)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Link: exact page (YOU)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Status (YOU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>EXAMPLE</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Example Lake State Park</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/example</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Grounds 06:00-22:00 Eastern</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/example/hours</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>US-1273</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Barren River Lake State Park</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/lucas/parks/resort/barren-river-lake-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>US-1274</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Blue Licks Battlefield State Park</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/carlisle/parks/historic/blue-licks-battlefield-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>US-3781</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Breaks Interstate State Park</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.breakspark.com/</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>US-1275</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Buckhorn Lake State Park</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>https://next.pota.app/park/US-1275</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>US-1251</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carr Creek State Park</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>https://next.pota.app/park/US-1251</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>US-1276</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Carter Caves State Park</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/olive-hill/parks/resort/carter-caves-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>US-1277</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Cumberland Falls State Park</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/corbin/parks/resort/cumberland-falls-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>US-1278</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Dale Hollow State Park</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/burkesville/parks/resort/dale-hollow-lake-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>US-1254</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>E.P. 'Tom' Sawyer State Park</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/explore/e-p-tom-sawyer-state-park-7810</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>US-1257</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>General Burnside State Park</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/burnside/parks/recreation/general-burnside-island-state-park</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>US-1279</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>General Butler State Park</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/carrollton/parks/historic/general-butler-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>US-1258</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Grayson Lake State Park</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/olive-hill/parks/recreation/grayson-lake-state-park</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>US-1280</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Greenbo Lake State Park</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/ashland/parks/historic/greenbo-lake-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>US-1281</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Jenny Wiley State Park</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/prestonsburg/parks/resort/jenny-wiley-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>US-1282</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Kenlake State Park</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/hardin/parks/resort/kenlake-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>US-1283</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Kentucky Dam Village State Park</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/gilbertsville/parks/resort/kentucky-dam-village-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>US-1261</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Kincaid Lake State Park</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/falmouth/parks/recreation/kincaid-lake-state-park</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>US-1262</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Kingdom Come State Park</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/cumberland/parks/recreation/kingdom-come-state-park</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>US-1284</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Lake Barkley State Park</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/cadiz/parks/resort/lake-barkley-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>US-1285</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Lake Cumberland State Park</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/jamestown/parks/resort/lake-cumberland-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr"/>
+      <c r="G22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>US-1263</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Lake Malone State Park</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/dunmor/parks/recreation/lake-malone-state-park</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>US-1264</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Levi Jackson Wilderness Road State Park</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://levijacksonpark.com/</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>US-1266</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Mineral Mounds State Park</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/eddyville/parks/recreation/mineral-mound-state-park</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>US-1267</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>My Old Kentucky Home State Park</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/bardstown/parks/historic/my-old-kentucky-home-state-park</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>US-1286</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Natural Bridge State Park</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/slade/parks/resort/natural-bridge-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>US-1268</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Nolin Lake State Park</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/mammoth-cave/parks/recreation/nolin-lake-state-park</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr"/>
+      <c r="G28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>US-1270</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Paintsville Lake State Park</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/staffordsville/parks/recreation/paintsville-lake-state-park</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>US-1287</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Pennyrile Forest State Park</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/dawson-springs/parks/resort/pennyrile-forest-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr"/>
+      <c r="G30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>US-1288</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Pine Mountain State Park</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/pineville/parks/resort/pine-mountain-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>US-1289</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Rough River Dam State Park</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/falls-rough/parks/resort/rough-river-dam-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr"/>
+      <c r="F32" s="8" t="inlineStr"/>
+      <c r="G32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>US-1271</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Taylorsville Lake State Park</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/mount-eden/parks/recreation/taylorsville-lake-state-park</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>US-1272</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Yatesville Lake State Park</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>State Park</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/louisa/parks/recreation/yatesville-lake-state-park</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr"/>
+      <c r="G34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>US-7966</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Bad Branch State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Bad-Branch.aspx</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr"/>
+      <c r="G35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>US-12971</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Bat Cave State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Carter-Caves.aspx</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr"/>
+      <c r="G36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>US-7956</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Beargrass Creek State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Beargrass-Creek.aspx</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>US-7954</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Blackacre State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Blackacre.aspx</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr"/>
+      <c r="G38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>US-7967</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Blanton Forest State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Blanton-Forest.aspx</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>US-7965</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Brigadoon State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Brigadoon.aspx</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr"/>
+      <c r="F40" s="8" t="inlineStr"/>
+      <c r="G40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>US-12972</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Cascade Caverns State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>https://opengisdata.ky.gov/datasets/ky-knp-state-nature-preserves/explore?location=38.354945%2C-83.108279%2C14.97</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>US-7960</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Crooked Creek State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Crooked-Creek.aspx</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr"/>
+      <c r="G42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>US-7968</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>E. Lucy Braun State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/E.-Lucy-Braun.aspx</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>US-12752</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Green River State Natural Area</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Rush-Island-Bottoms.aspx</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
+      <c r="G44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>US-7957</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Hall-Hill/Vernon-Douglas State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Vernon-Douglas.aspx</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>US-7961</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Jesse Stuart State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Jesse-Stuart.aspx</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr"/>
+      <c r="G46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>US-7958</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Kentucky River Palisades/Tom Dorman State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Tom-Dorman.aspx</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>US-7962</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Little South Fork State Natural Area</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Burnett-WWCA.aspx</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr"/>
+      <c r="F48" s="8" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>US-7953</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Metropolis Lake State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Metropolis-Lake.aspx</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr"/>
+      <c r="F49" s="8" t="inlineStr"/>
+      <c r="G49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>US-7963</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Pilot Knob State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Pilot-Knob.aspx</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr"/>
+      <c r="F50" s="8" t="inlineStr"/>
+      <c r="G50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>US-7959</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Quiet Trails State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Quiet-Trails.aspx</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr"/>
+      <c r="F51" s="8" t="inlineStr"/>
+      <c r="G51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>US-7970</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Sinking Creek State Natural Area</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Sinking-Creek.aspx</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr"/>
+      <c r="F52" s="8" t="inlineStr"/>
+      <c r="G52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>US-7955</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Six Mile Island State Nature Preserve</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Six-Mile-Island.aspx</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr"/>
+      <c r="G53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>US-7964</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>William H. Martin State Natural Area</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Nature Preserve</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Dr.-William-H.-Martin-WWCA.aspx</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr"/>
+      <c r="F54" s="8" t="inlineStr"/>
+      <c r="G54" s="8" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>US-7951</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Green River State Forest</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Green-River-State-Forest.aspx</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr"/>
+      <c r="F55" s="8" t="inlineStr"/>
+      <c r="G55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>US-4688</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Kentenia State Forest</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Kentenia-State-Forest.aspx</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr"/>
+      <c r="F56" s="8" t="inlineStr"/>
+      <c r="G56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>US-4689</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Kentucky Ridge State Forest</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Kentucky-Ridge-State-Forest.aspx</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr"/>
+      <c r="F57" s="8" t="inlineStr"/>
+      <c r="G57" s="8" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>US-4690</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Knobs State Forest</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Knobs-State-Forest-and-Wildlife-Management-Area.aspx</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr"/>
+      <c r="F58" s="8" t="inlineStr"/>
+      <c r="G58" s="8" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>US-7952</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Marrowbone State Forest</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/MarrowboneStateForestandWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr"/>
+      <c r="F59" s="8" t="inlineStr"/>
+      <c r="G59" s="8" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>US-4692</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Pennyrile State Forest</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/dawson-springs/parks/resort/pennyrile-forest-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr"/>
+      <c r="F60" s="8" t="inlineStr"/>
+      <c r="G60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>US-4693</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Tygarts State Forest</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Tygarts-State-Forest.aspx</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr"/>
+      <c r="F61" s="8" t="inlineStr"/>
+      <c r="G61" s="8" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>US-10102</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Pine Mountain State Trail</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/whitesburg/parks/recreation/pine-mountain-state-scenic-trail</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr"/>
+      <c r="F62" s="8" t="inlineStr"/>
+      <c r="G62" s="8" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>US-11181</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Sheltowee Trace National Recreation Trail</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fs.usda.gov/wildflowers/regions/southern/SheltoweeTrace/index.shtml</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr"/>
+      <c r="F63" s="8" t="inlineStr"/>
+      <c r="G63" s="8" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>US-13598</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Beaver Lake State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=49</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr"/>
+      <c r="F64" s="8" t="inlineStr"/>
+      <c r="G64" s="8" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>US-13607</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Boltz State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=50</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr"/>
+      <c r="F65" s="8" t="inlineStr"/>
+      <c r="G65" s="8" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>US-13606</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Bullock Pen State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=51</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr"/>
+      <c r="F66" s="8" t="inlineStr"/>
+      <c r="G66" s="8" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>US-13600</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Carpenters Lake State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=39</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr"/>
+      <c r="F67" s="8" t="inlineStr"/>
+      <c r="G67" s="8" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>US-13601</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Guist Creek Lake State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=56</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr"/>
+      <c r="F68" s="8" t="inlineStr"/>
+      <c r="G68" s="8" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>US-13599</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Kingfisher Lakes State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=40</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr"/>
+      <c r="F69" s="8" t="inlineStr"/>
+      <c r="G69" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/.claude/build/research/KPC_Park_Hours_worklist.xlsx
+++ b/.claude/build/research/KPC_Park_Hours_worklist.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Hours + fees (40)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Hours only (67)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KY parks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -488,7 +487,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KPC park hours and fees: the 40 Kentucky parks most likely to charge or keep hours (most Kentucky parks are free and open, so they are not on this list)</t>
+          <t>KPC park hours, after-dark access and fees: every Kentucky POTA park we still need (most Kentucky parks are free, so a fee is often $0.00 or not mentioned)</t>
         </is>
       </c>
     </row>
@@ -522,31 +521,31 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Fee: what it costs to get in, e.g. $0.00 or $5.00 per car. If only some day-use areas charge (Land Between the Lakes, national forests), name them, e.g. "$5.00 at Hillman Ferry day-use; rest free"</t>
+          <t xml:space="preserve">  • After dark: can you stay after dark or overnight? yes / no / campground only</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • Fee: what it costs to get in, e.g. $0.00 or $5.00 per car. If only some areas charge (Land Between the Lakes, national forests), name them. If the page says nothing about a fee, leave it empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • Link: the exact page where you saw it</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Rules: official pages only (parks.ky.gov, eec.ky.gov, fw.ky.gov, nps.gov, fs.usda.gov, fws.gov, the park's own site). Only what the page says. Not there = leave it empty and write NOT ON PAGE in Status. No new tabs or columns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>TAB 2 "Hours only": after the first tab is done, do these the same way, but HOURS ONLY (these parks are free, skip the fee). Same Status rule: start at the first row with an empty Status.</t>
         </is>
       </c>
     </row>
@@ -561,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:I181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -569,9 +568,10 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,15 +602,20 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>After dark / overnight (YOU)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
           <t>Fee (YOU)</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Link: exact page (YOU)</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Status (YOU)</t>
         </is>
@@ -639,20 +644,25 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Dawn to dusk</t>
+          <t>Grounds 06:00-22:00 Eastern</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
+          <t>Campground only</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
           <t>$0.00</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>https://parks.ky.gov/example/hours</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -661,2274 +671,1227 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>US-0724</t>
+          <t>US-1273</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Abraham Lincoln Birthplace National Historic Site</t>
+          <t>Barren River Lake State Park</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.nps.gov/abli/index.htm</t>
+          <t>https://parks.ky.gov/lucas/parks/resort/barren-river-lake-state-resort-park</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr"/>
       <c r="F3" s="8" t="inlineStr"/>
       <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>US-10112</t>
+          <t>US-1274</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bad Branch National Wild and Scenic River</t>
+          <t>Blue Licks Battlefield State Park</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Bad-Branch-Wild-River.aspx</t>
+          <t>https://parks.ky.gov/carlisle/parks/historic/blue-licks-battlefield-state-resort-park</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr"/>
       <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>US-10107</t>
+          <t>US-3781</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Big South Fork National Wild and Scenic River</t>
+          <t>Breaks Interstate State Park</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Big-South-Fork-Wild-River.aspx</t>
+          <t>https://www.breakspark.com/</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>US-7950</t>
+          <t>US-1275</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Camp Nelson National Monument</t>
+          <t>Buckhorn Lake State Park</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.nps.gov/cane/index.htm</t>
+          <t>https://next.pota.app/park/US-1275</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
       <c r="G6" s="8" t="inlineStr"/>
       <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>US-0295</t>
+          <t>US-1251</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Clarks River National Wildlife Refuge</t>
+          <t>Carr Creek State Park</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fws.gov/refuge/clarks-river</t>
+          <t>https://next.pota.app/park/US-1251</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr"/>
       <c r="F7" s="8" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>US-0019</t>
+          <t>US-1276</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cumberland Gap National Historical Park</t>
+          <t>Carter Caves State Park</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://www.nps.gov/cuga/index.htm</t>
+          <t>https://parks.ky.gov/olive-hill/parks/resort/carter-caves-state-resort-park</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr"/>
       <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr"/>
       <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>US-0703</t>
+          <t>US-1277</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Fort Donelson National Battlefield</t>
+          <t>Cumberland Falls State Park</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://next.pota.app/park/US-0703</t>
+          <t>https://parks.ky.gov/corbin/parks/resort/cumberland-falls-state-resort-park</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>US-3790</t>
+          <t>US-1278</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Fort Heiman National Battlefield</t>
+          <t>Dale Hollow State Park</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://www.nps.gov/fodo/planyourvisit/maps.htm</t>
+          <t>https://parks.ky.gov/burkesville/parks/resort/dale-hollow-lake-state-resort-park</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr"/>
       <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="8" t="inlineStr"/>
       <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>US-10098</t>
+          <t>US-1254</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Green River National Wildlife Refuge</t>
+          <t>E.P. 'Tom' Sawyer State Park</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://www.fws.gov/refuge/green-river/visit-us/locations/green-river-national-wildlife-refuge</t>
+          <t>https://parks.ky.gov/explore/e-p-tom-sawyer-state-park-7810</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
       <c r="F11" s="8" t="inlineStr"/>
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>US-4572</t>
+          <t>US-1257</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Lewis and Clark National Historic Trail</t>
+          <t>General Burnside State Park</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://www.nps.gov/lecl/index.htm</t>
+          <t>https://parks.ky.gov/burnside/parks/recreation/general-burnside-island-state-park</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr"/>
       <c r="F12" s="8" t="inlineStr"/>
       <c r="G12" s="8" t="inlineStr"/>
       <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>US-7708</t>
+          <t>US-1279</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Mill Springs Battlefield National Monument</t>
+          <t>General Butler State Park</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://www.nps.gov/misp/index.htm</t>
+          <t>https://parks.ky.gov/carrollton/parks/historic/general-butler-state-resort-park</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr"/>
       <c r="F13" s="8" t="inlineStr"/>
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>US-0608</t>
+          <t>US-1258</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ohio River Islands National Wildlife Refuge</t>
+          <t>Grayson Lake State Park</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://www.fws.gov/refuge/ohio-river-islands</t>
+          <t>https://parks.ky.gov/olive-hill/parks/recreation/grayson-lake-state-park</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr"/>
       <c r="F14" s="8" t="inlineStr"/>
       <c r="G14" s="8" t="inlineStr"/>
       <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>US-10104</t>
+          <t>US-1280</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Red River National Wild and Scenic River</t>
+          <t>Greenbo Lake State Park</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://www.fs.usda.gov/recarea/dbnf/recreation/recarea/?recid=39548</t>
+          <t>https://parks.ky.gov/ashland/parks/historic/greenbo-lake-state-resort-park</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="8" t="inlineStr"/>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>US-0538</t>
+          <t>US-1281</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Reelfoot National Wildlife Refuge</t>
+          <t>Jenny Wiley State Park</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://www.fws.gov/refuge/reelfoot/</t>
+          <t>https://parks.ky.gov/prestonsburg/parks/resort/jenny-wiley-state-resort-park</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr"/>
       <c r="F16" s="8" t="inlineStr"/>
       <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>US-10111</t>
+          <t>US-1282</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Rock Creek National Wild and Scenic River</t>
+          <t>Kenlake State Park</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Rock-Creek-Wild-River.aspx</t>
+          <t>https://parks.ky.gov/hardin/parks/resort/kenlake-state-resort-park</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
       <c r="F17" s="8" t="inlineStr"/>
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>US-10105</t>
+          <t>US-1283</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>The Green National Wild and Scenic River</t>
+          <t>Kentucky Dam Village State Park</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Green-River-Wild-River.aspx</t>
+          <t>https://parks.ky.gov/gilbertsville/parks/resort/kentucky-dam-village-state-resort-park</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr"/>
       <c r="F18" s="8" t="inlineStr"/>
       <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>US-10106</t>
+          <t>US-1261</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>The Rockcastle National Wild and Scenic River</t>
+          <t>Kincaid Lake State Park</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Rockcastle-River-Wild-River.aspx</t>
+          <t>https://parks.ky.gov/falmouth/parks/recreation/kincaid-lake-state-park</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
       <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>US-3791</t>
+          <t>US-1262</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Trail of Tears National Historic Trail</t>
+          <t>Kingdom Come State Park</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>National / NPS</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://www.nps.gov/trte/index.htm</t>
+          <t>https://parks.ky.gov/cumberland/parks/recreation/kingdom-come-state-park</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
       <c r="F20" s="8" t="inlineStr"/>
       <c r="G20" s="8" t="inlineStr"/>
       <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>US-0050</t>
+          <t>US-1284</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Mammoth Cave National Park</t>
+          <t>Lake Barkley State Park</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>National Park</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://www.nps.gov/maca/index.htm</t>
+          <t>https://parks.ky.gov/cadiz/parks/resort/lake-barkley-state-resort-park</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>US-3779</t>
+          <t>US-1285</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Big Bone Lick State Historic Site</t>
+          <t>Lake Cumberland State Park</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>https://parks.ky.gov/union/parks/historic/big-bone-lick-state-historic-site</t>
+          <t>https://parks.ky.gov/jamestown/parks/resort/lake-cumberland-state-resort-park</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr"/>
       <c r="F22" s="8" t="inlineStr"/>
       <c r="G22" s="8" t="inlineStr"/>
       <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>US-3782</t>
+          <t>US-1263</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Dr. Thomas Walker State Historic Site</t>
+          <t>Lake Malone State Park</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>https://parks.ky.gov/barbourville/parks/historic/dr-thomas-walker-state-historic-site</t>
+          <t>https://parks.ky.gov/dunmor/parks/recreation/lake-malone-state-park</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr"/>
       <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>US-7890</t>
+          <t>US-1264</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Isaac Shelby Cemetery State Historic Site</t>
+          <t>Levi Jackson Wilderness Road State Park</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>https://next.pota.app/park/US-7890</t>
+          <t>https://levijacksonpark.com/</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
       <c r="F24" s="8" t="inlineStr"/>
       <c r="G24" s="8" t="inlineStr"/>
       <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>US-3783</t>
+          <t>US-1266</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Jefferson Davis State Historic Site</t>
+          <t>Mineral Mounds State Park</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>https://parks.ky.gov/fairview/parks/historic/jefferson-davis-state-historic-site</t>
+          <t>https://parks.ky.gov/eddyville/parks/recreation/mineral-mound-state-park</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr"/>
       <c r="F25" s="8" t="inlineStr"/>
       <c r="G25" s="8" t="inlineStr"/>
       <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>US-3784</t>
+          <t>US-1267</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Old Mulkey Meetinghouse State Historic Site</t>
+          <t>My Old Kentucky Home State Park</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>https://parks.ky.gov/tompkinsville/parks/historic/old-mulkey-meetinghouse-state-historic-site</t>
+          <t>https://parks.ky.gov/bardstown/parks/historic/my-old-kentucky-home-state-park</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr"/>
       <c r="F26" s="8" t="inlineStr"/>
       <c r="G26" s="8" t="inlineStr"/>
       <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>US-3785</t>
+          <t>US-1286</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Perryville Battlefield State Historic Site</t>
+          <t>Natural Bridge State Park</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>https://parks.ky.gov/perryville/parks/historic/perryville-battlefield-state-historic-site</t>
+          <t>https://parks.ky.gov/slade/parks/resort/natural-bridge-state-resort-park</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
       <c r="F27" s="8" t="inlineStr"/>
       <c r="G27" s="8" t="inlineStr"/>
       <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>US-10172</t>
+          <t>US-1268</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Salato Wildlife Refuge</t>
+          <t>Nolin Lake State Park</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>https://fw.ky.gov/Education/Pages/Salato-Wildlife-Education-Center.aspx</t>
+          <t>https://parks.ky.gov/mammoth-cave/parks/recreation/nolin-lake-state-park</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
       <c r="F28" s="8" t="inlineStr"/>
       <c r="G28" s="8" t="inlineStr"/>
       <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>US-3786</t>
+          <t>US-1270</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Waveland State Historic Site</t>
+          <t>Paintsville Lake State Park</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>https://parks.ky.gov/lexington/parks/historic/waveland-state-historic-site</t>
+          <t>https://parks.ky.gov/staffordsville/parks/recreation/paintsville-lake-state-park</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr"/>
       <c r="F29" s="8" t="inlineStr"/>
       <c r="G29" s="8" t="inlineStr"/>
       <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>US-3787</t>
+          <t>US-1287</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>White Hall State Historic Site</t>
+          <t>Pennyrile Forest State Park</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>https://whitehall.eku.edu</t>
+          <t>https://parks.ky.gov/dawson-springs/parks/resort/pennyrile-forest-state-resort-park</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
       <c r="F30" s="8" t="inlineStr"/>
       <c r="G30" s="8" t="inlineStr"/>
       <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>US-3788</t>
+          <t>US-1288</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Wickliffe Mounds State Historic Site</t>
+          <t>Pine Mountain State Park</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>https://parks.ky.gov/wickliffe/parks/historic/wickliffe-mounds-state-historic-site</t>
+          <t>https://parks.ky.gov/pineville/parks/resort/pine-mountain-state-resort-park</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr"/>
       <c r="F31" s="8" t="inlineStr"/>
       <c r="G31" s="8" t="inlineStr"/>
       <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>US-3789</t>
+          <t>US-1289</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>William Whitley House State Historic Site</t>
+          <t>Rough River Dam State Park</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>https://explorekyhistory.ky.gov/files/show/236</t>
+          <t>https://parks.ky.gov/falls-rough/parks/resort/rough-river-dam-state-resort-park</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr"/>
       <c r="F32" s="8" t="inlineStr"/>
       <c r="G32" s="8" t="inlineStr"/>
       <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>US-0686</t>
+          <t>US-1271</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Big South Fork National Recreation Area</t>
+          <t>Taylorsville Lake State Park</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>National Recreation Area</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>https://www.nps.gov/biso/index.htm</t>
+          <t>https://parks.ky.gov/mount-eden/parks/recreation/taylorsville-lake-state-park</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr"/>
       <c r="F33" s="8" t="inlineStr"/>
       <c r="G33" s="8" t="inlineStr"/>
       <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>US-3801</t>
+          <t>US-1272</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Clifty Wilderness Area</t>
+          <t>Yatesville Lake State Park</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>River / Wilderness</t>
+          <t>State Park</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>https://www.fs.usda.gov/recarea/dbnf/recarea/?recid=39460</t>
+          <t>https://parks.ky.gov/louisa/parks/recreation/yatesville-lake-state-park</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr"/>
       <c r="F34" s="8" t="inlineStr"/>
       <c r="G34" s="8" t="inlineStr"/>
       <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>US-3802</t>
+          <t>US-10112</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Clyde E Buckley Sanctuary</t>
+          <t>Bad Branch National Wild and Scenic River</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Sanctuary</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>https://bggreensource.org/buckley/</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Bad-Branch-Wild-River.aspx</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr"/>
       <c r="F35" s="8" t="inlineStr"/>
       <c r="G35" s="8" t="inlineStr"/>
       <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>US-4484</t>
+          <t>US-10107</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Daniel Boone National Forest</t>
+          <t>Big South Fork National Wild and Scenic River</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>National Forest</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>https://www.fs.usda.gov/dbnf/</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Big-South-Fork-Wild-River.aspx</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr"/>
       <c r="F36" s="8" t="inlineStr"/>
       <c r="G36" s="8" t="inlineStr"/>
       <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>US-4526</t>
+          <t>US-7950</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>George Washington &amp; Jefferson National Forest</t>
+          <t>Camp Nelson National Monument</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>National Forest</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>https://www.fs.usda.gov/gwj</t>
+          <t>https://www.nps.gov/cane/index.htm</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr"/>
       <c r="G37" s="8" t="inlineStr"/>
       <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>US-10173</t>
+          <t>US-3790</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Kentucky Horse Park</t>
+          <t>Fort Heiman National Battlefield</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>State Facility</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>https://www.kyhorsepark.com/</t>
+          <t>https://www.nps.gov/fodo/planyourvisit/maps.htm</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr"/>
       <c r="F38" s="8" t="inlineStr"/>
       <c r="G38" s="8" t="inlineStr"/>
       <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>US-3792</t>
+          <t>US-10098</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Land Between the Lakes National Recreation Area</t>
+          <t>Green River National Wildlife Refuge</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>National Recreation Area</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>https://landbetweenthelakes.us/</t>
+          <t>https://www.fws.gov/refuge/green-river/visit-us/locations/green-river-national-wildlife-refuge</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr"/>
       <c r="G39" s="8" t="inlineStr"/>
       <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>US-8144</t>
+          <t>US-4572</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Otter Creek State Recreation Area</t>
+          <t>Lewis and Clark National Historic Trail</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Recreation Area</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>https://fw.ky.gov/Pages/Otter-Creek-Outdoor-Recreation-Area.aspx</t>
+          <t>https://www.nps.gov/lecl/index.htm</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr"/>
       <c r="F40" s="8" t="inlineStr"/>
       <c r="G40" s="8" t="inlineStr"/>
       <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>US-10103</t>
+          <t>US-7708</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>The Cumberland River Wilderness Area</t>
+          <t>Mill Springs Battlefield National Monument</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>River / Wilderness</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Cumberland-River-Wild-River.aspx</t>
+          <t>https://www.nps.gov/misp/index.htm</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr"/>
       <c r="G41" s="8" t="inlineStr"/>
       <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>US-10099</t>
+          <t>US-10104</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Wolf Creek National Fish Hatchery</t>
+          <t>Red River National Wild and Scenic River</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Fish Hatchery</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>https://www.fws.gov/fish-hatchery/wolf-creek/map</t>
+          <t>https://www.fs.usda.gov/recarea/dbnf/recreation/recarea/?recid=39548</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr"/>
       <c r="F42" s="8" t="inlineStr"/>
       <c r="G42" s="8" t="inlineStr"/>
       <c r="H42" s="8" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Park ref</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Park name</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Kind</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Our link</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Hours (YOU)</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Link: exact page (YOU)</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Status (YOU)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>EXAMPLE</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Example Lake State Park</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/example</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Grounds 06:00-22:00 Eastern</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/example/hours</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>US-1273</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Barren River Lake State Park</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/lucas/parks/resort/barren-river-lake-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>US-1274</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Blue Licks Battlefield State Park</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/carlisle/parks/historic/blue-licks-battlefield-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>US-3781</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Breaks Interstate State Park</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>https://www.breakspark.com/</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>US-1275</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Buckhorn Lake State Park</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>https://next.pota.app/park/US-1275</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>US-1251</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Carr Creek State Park</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>https://next.pota.app/park/US-1251</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>US-1276</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Carter Caves State Park</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/olive-hill/parks/resort/carter-caves-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>US-1277</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Cumberland Falls State Park</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/corbin/parks/resort/cumberland-falls-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>US-1278</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Dale Hollow State Park</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/burkesville/parks/resort/dale-hollow-lake-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>US-1254</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>E.P. 'Tom' Sawyer State Park</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/explore/e-p-tom-sawyer-state-park-7810</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>US-1257</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>General Burnside State Park</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/burnside/parks/recreation/general-burnside-island-state-park</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>US-1279</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>General Butler State Park</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/carrollton/parks/historic/general-butler-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>US-1258</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Grayson Lake State Park</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/olive-hill/parks/recreation/grayson-lake-state-park</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>US-1280</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Greenbo Lake State Park</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/ashland/parks/historic/greenbo-lake-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>US-1281</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Jenny Wiley State Park</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/prestonsburg/parks/resort/jenny-wiley-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>US-1282</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Kenlake State Park</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/hardin/parks/resort/kenlake-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>US-1283</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Kentucky Dam Village State Park</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/gilbertsville/parks/resort/kentucky-dam-village-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>US-1261</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Kincaid Lake State Park</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/falmouth/parks/recreation/kincaid-lake-state-park</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>US-1262</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Kingdom Come State Park</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/cumberland/parks/recreation/kingdom-come-state-park</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>US-1284</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Lake Barkley State Park</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/cadiz/parks/resort/lake-barkley-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>US-1285</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Lake Cumberland State Park</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/jamestown/parks/resort/lake-cumberland-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>US-1263</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Lake Malone State Park</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/dunmor/parks/recreation/lake-malone-state-park</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>US-1264</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Levi Jackson Wilderness Road State Park</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://levijacksonpark.com/</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>US-1266</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Mineral Mounds State Park</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/eddyville/parks/recreation/mineral-mound-state-park</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>US-1267</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>My Old Kentucky Home State Park</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/bardstown/parks/historic/my-old-kentucky-home-state-park</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr"/>
-      <c r="F26" s="8" t="inlineStr"/>
-      <c r="G26" s="8" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>US-1286</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Natural Bridge State Park</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/slade/parks/resort/natural-bridge-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>US-1268</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Nolin Lake State Park</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/mammoth-cave/parks/recreation/nolin-lake-state-park</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr"/>
-      <c r="G28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>US-1270</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Paintsville Lake State Park</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/staffordsville/parks/recreation/paintsville-lake-state-park</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="8" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>US-1287</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Pennyrile Forest State Park</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/dawson-springs/parks/resort/pennyrile-forest-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr"/>
-      <c r="G30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>US-1288</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Pine Mountain State Park</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/pineville/parks/resort/pine-mountain-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>US-1289</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Rough River Dam State Park</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/falls-rough/parks/resort/rough-river-dam-state-resort-park</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>US-1271</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Taylorsville Lake State Park</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/mount-eden/parks/recreation/taylorsville-lake-state-park</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr"/>
-      <c r="G33" s="8" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>US-1272</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Yatesville Lake State Park</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>State Park</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>https://parks.ky.gov/louisa/parks/recreation/yatesville-lake-state-park</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr"/>
-      <c r="G34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>US-7966</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Bad Branch State Nature Preserve</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Nature Preserve</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Bad-Branch.aspx</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr"/>
-      <c r="G35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>US-12971</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Bat Cave State Nature Preserve</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Nature Preserve</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Carter-Caves.aspx</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr"/>
-      <c r="F36" s="8" t="inlineStr"/>
-      <c r="G36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>US-7956</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Beargrass Creek State Nature Preserve</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Nature Preserve</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Beargrass-Creek.aspx</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr"/>
-      <c r="G37" s="8" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>US-7954</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Blackacre State Nature Preserve</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Nature Preserve</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Blackacre.aspx</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr"/>
-      <c r="F38" s="8" t="inlineStr"/>
-      <c r="G38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>US-7967</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Blanton Forest State Nature Preserve</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Nature Preserve</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Blanton-Forest.aspx</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr"/>
-      <c r="F39" s="8" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>US-7965</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Brigadoon State Nature Preserve</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Nature Preserve</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Brigadoon.aspx</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>US-12972</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Cascade Caverns State Nature Preserve</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Nature Preserve</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>https://opengisdata.ky.gov/datasets/ky-knp-state-nature-preserves/explore?location=38.354945%2C-83.108279%2C14.97</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr"/>
-      <c r="F41" s="8" t="inlineStr"/>
-      <c r="G41" s="8" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>US-7960</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Crooked Creek State Nature Preserve</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Nature Preserve</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Crooked-Creek.aspx</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr"/>
-      <c r="F42" s="8" t="inlineStr"/>
-      <c r="G42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>US-7968</t>
+          <t>US-0538</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>E. Lucy Braun State Nature Preserve</t>
+          <t>Reelfoot National Wildlife Refuge</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Nature Preserve</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/E.-Lucy-Braun.aspx</t>
+          <t>https://www.fws.gov/refuge/reelfoot/</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr"/>
       <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>US-12752</t>
+          <t>US-10111</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Green River State Natural Area</t>
+          <t>Rock Creek National Wild and Scenic River</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Nature Preserve</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Rush-Island-Bottoms.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Rock-Creek-Wild-River.aspx</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr"/>
       <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>US-7957</t>
+          <t>US-10105</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Hall-Hill/Vernon-Douglas State Nature Preserve</t>
+          <t>The Green National Wild and Scenic River</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Nature Preserve</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Vernon-Douglas.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Green-River-Wild-River.aspx</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr"/>
       <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>US-7961</t>
+          <t>US-10106</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Jesse Stuart State Nature Preserve</t>
+          <t>The Rockcastle National Wild and Scenic River</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Nature Preserve</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Jesse-Stuart.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Rockcastle-River-Wild-River.aspx</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr"/>
       <c r="F46" s="8" t="inlineStr"/>
       <c r="G46" s="8" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>US-7958</t>
+          <t>US-3791</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Kentucky River Palisades/Tom Dorman State Nature Preserve</t>
+          <t>Trail of Tears National Historic Trail</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Nature Preserve</t>
+          <t>National / NPS</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Tom-Dorman.aspx</t>
+          <t>https://www.nps.gov/trte/index.htm</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr"/>
       <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>US-7962</t>
+          <t>US-7966</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Little South Fork State Natural Area</t>
+          <t>Bad Branch State Nature Preserve</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -2938,22 +1901,24 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Burnett-WWCA.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Bad-Branch.aspx</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr"/>
       <c r="F48" s="8" t="inlineStr"/>
       <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>US-7953</t>
+          <t>US-12971</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Metropolis Lake State Nature Preserve</t>
+          <t>Bat Cave State Nature Preserve</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -2963,22 +1928,24 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Metropolis-Lake.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Carter-Caves.aspx</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr"/>
       <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>US-7963</t>
+          <t>US-7956</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Pilot Knob State Nature Preserve</t>
+          <t>Beargrass Creek State Nature Preserve</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -2988,22 +1955,24 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Pilot-Knob.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Beargrass-Creek.aspx</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr"/>
       <c r="F50" s="8" t="inlineStr"/>
       <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>US-7959</t>
+          <t>US-7954</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Quiet Trails State Nature Preserve</t>
+          <t>Blackacre State Nature Preserve</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -3013,22 +1982,24 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Quiet-Trails.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Blackacre.aspx</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr"/>
       <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>US-7970</t>
+          <t>US-7967</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Sinking Creek State Natural Area</t>
+          <t>Blanton Forest State Nature Preserve</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -3038,22 +2009,24 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Sinking-Creek.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Blanton-Forest.aspx</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr"/>
       <c r="F52" s="8" t="inlineStr"/>
       <c r="G52" s="8" t="inlineStr"/>
+      <c r="H52" s="8" t="inlineStr"/>
+      <c r="I52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>US-7955</t>
+          <t>US-7965</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Six Mile Island State Nature Preserve</t>
+          <t>Brigadoon State Nature Preserve</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -3063,22 +2036,24 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Six-Mile-Island.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Brigadoon.aspx</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr"/>
       <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>US-7964</t>
+          <t>US-12972</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>William H. Martin State Natural Area</t>
+          <t>Cascade Caverns State Nature Preserve</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -3088,387 +2063,3443 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Dr.-William-H.-Martin-WWCA.aspx</t>
+          <t>https://opengisdata.ky.gov/datasets/ky-knp-state-nature-preserves/explore?location=38.354945%2C-83.108279%2C14.97</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="8" t="inlineStr"/>
       <c r="G54" s="8" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>US-7951</t>
+          <t>US-7960</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Green River State Forest</t>
+          <t>Crooked Creek State Nature Preserve</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>State Forest</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Green-River-State-Forest.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Crooked-Creek.aspx</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr"/>
       <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>US-4688</t>
+          <t>US-7968</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Kentenia State Forest</t>
+          <t>E. Lucy Braun State Nature Preserve</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>State Forest</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Kentenia-State-Forest.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/E.-Lucy-Braun.aspx</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="inlineStr"/>
       <c r="G56" s="8" t="inlineStr"/>
+      <c r="H56" s="8" t="inlineStr"/>
+      <c r="I56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>US-4689</t>
+          <t>US-12752</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Kentucky Ridge State Forest</t>
+          <t>Green River State Natural Area</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>State Forest</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Kentucky-Ridge-State-Forest.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Rush-Island-Bottoms.aspx</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr"/>
       <c r="G57" s="8" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>US-4690</t>
+          <t>US-7957</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Knobs State Forest</t>
+          <t>Hall-Hill/Vernon-Douglas State Nature Preserve</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>State Forest</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Knobs-State-Forest-and-Wildlife-Management-Area.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Vernon-Douglas.aspx</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr"/>
       <c r="G58" s="8" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>US-7952</t>
+          <t>US-7961</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Marrowbone State Forest</t>
+          <t>Jesse Stuart State Nature Preserve</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>State Forest</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>https://fw.ky.gov/More/Documents/MarrowboneStateForestandWMA_ALL.pdf</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Jesse-Stuart.aspx</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr"/>
       <c r="G59" s="8" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>US-4692</t>
+          <t>US-7958</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Pennyrile State Forest</t>
+          <t>Kentucky River Palisades/Tom Dorman State Nature Preserve</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>State Forest</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>https://parks.ky.gov/dawson-springs/parks/resort/pennyrile-forest-state-resort-park</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Tom-Dorman.aspx</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr"/>
       <c r="G60" s="8" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>US-4693</t>
+          <t>US-7962</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Tygarts State Forest</t>
+          <t>Little South Fork State Natural Area</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>State Forest</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Tygarts-State-Forest.aspx</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Burnett-WWCA.aspx</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr"/>
       <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr"/>
+      <c r="I61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>US-10102</t>
+          <t>US-7953</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Pine Mountain State Trail</t>
+          <t>Metropolis Lake State Nature Preserve</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Trail</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>https://parks.ky.gov/whitesburg/parks/recreation/pine-mountain-state-scenic-trail</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Metropolis-Lake.aspx</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="8" t="inlineStr"/>
       <c r="G62" s="8" t="inlineStr"/>
+      <c r="H62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>US-11181</t>
+          <t>US-7963</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Sheltowee Trace National Recreation Trail</t>
+          <t>Pilot Knob State Nature Preserve</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Trail</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>https://www.fs.usda.gov/wildflowers/regions/southern/SheltoweeTrace/index.shtml</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Pilot-Knob.aspx</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr"/>
       <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>US-13598</t>
+          <t>US-7959</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Beaver Lake State Fishing Lake</t>
+          <t>Quiet Trails State Nature Preserve</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>State Fishing Lake</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=49</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Quiet-Trails.aspx</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="8" t="inlineStr"/>
       <c r="G64" s="8" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>US-13607</t>
+          <t>US-7970</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Boltz State Fishing Lake</t>
+          <t>Sinking Creek State Natural Area</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>State Fishing Lake</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=50</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Sinking-Creek.aspx</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr"/>
       <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>US-13606</t>
+          <t>US-7955</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Bullock Pen State Fishing Lake</t>
+          <t>Six Mile Island State Nature Preserve</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>State Fishing Lake</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=51</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Six-Mile-Island.aspx</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr"/>
       <c r="F66" s="8" t="inlineStr"/>
       <c r="G66" s="8" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>US-13600</t>
+          <t>US-7964</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Carpenters Lake State Fishing Lake</t>
+          <t>William H. Martin State Natural Area</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>State Fishing Lake</t>
+          <t>Nature Preserve</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=39</t>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Dr.-William-H.-Martin-WWCA.aspx</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr"/>
       <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>US-13601</t>
+          <t>US-7951</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Guist Creek Lake State Fishing Lake</t>
+          <t>Green River State Forest</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>State Fishing Lake</t>
+          <t>State Forest</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=56</t>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Green-River-State-Forest.aspx</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr"/>
       <c r="F68" s="8" t="inlineStr"/>
       <c r="G68" s="8" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>US-13599</t>
+          <t>US-4688</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Kingfisher Lakes State Fishing Lake</t>
+          <t>Kentenia State Forest</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>State Fishing Lake</t>
+          <t>State Forest</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=40</t>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Kentenia-State-Forest.aspx</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>US-4689</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Kentucky Ridge State Forest</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Kentucky-Ridge-State-Forest.aspx</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr"/>
+      <c r="F70" s="8" t="inlineStr"/>
+      <c r="G70" s="8" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>US-4690</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Knobs State Forest</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Knobs-State-Forest-and-Wildlife-Management-Area.aspx</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr"/>
+      <c r="F71" s="8" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>US-7952</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Marrowbone State Forest</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/MarrowboneStateForestandWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr"/>
+      <c r="F72" s="8" t="inlineStr"/>
+      <c r="G72" s="8" t="inlineStr"/>
+      <c r="H72" s="8" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>US-4692</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Pennyrile State Forest</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/dawson-springs/parks/resort/pennyrile-forest-state-resort-park</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr"/>
+      <c r="F73" s="8" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>US-4693</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Tygarts State Forest</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>State Forest</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Natural-Resources/Forestry/ky-state-forests/Pages/Tygarts-State-Forest.aspx</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr"/>
+      <c r="F74" s="8" t="inlineStr"/>
+      <c r="G74" s="8" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>US-3779</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Big Bone Lick State Historic Site</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/union/parks/historic/big-bone-lick-state-historic-site</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr"/>
+      <c r="F75" s="8" t="inlineStr"/>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr"/>
+      <c r="I75" s="8" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>US-3782</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Dr. Thomas Walker State Historic Site</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/barbourville/parks/historic/dr-thomas-walker-state-historic-site</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr"/>
+      <c r="F76" s="8" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>US-7890</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Isaac Shelby Cemetery State Historic Site</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>https://next.pota.app/park/US-7890</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr"/>
+      <c r="F77" s="8" t="inlineStr"/>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>US-3783</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Jefferson Davis State Historic Site</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/fairview/parks/historic/jefferson-davis-state-historic-site</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr"/>
+      <c r="F78" s="8" t="inlineStr"/>
+      <c r="G78" s="8" t="inlineStr"/>
+      <c r="H78" s="8" t="inlineStr"/>
+      <c r="I78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>US-3784</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Old Mulkey Meetinghouse State Historic Site</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/tompkinsville/parks/historic/old-mulkey-meetinghouse-state-historic-site</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr"/>
+      <c r="F79" s="8" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>US-3785</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Perryville Battlefield State Historic Site</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/perryville/parks/historic/perryville-battlefield-state-historic-site</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr"/>
+      <c r="F80" s="8" t="inlineStr"/>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>US-10172</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Salato Wildlife Refuge</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/Education/Pages/Salato-Wildlife-Education-Center.aspx</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr"/>
+      <c r="F81" s="8" t="inlineStr"/>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>US-3786</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Waveland State Historic Site</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/lexington/parks/historic/waveland-state-historic-site</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr"/>
+      <c r="F82" s="8" t="inlineStr"/>
+      <c r="G82" s="8" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr"/>
+      <c r="I82" s="8" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>US-3787</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>White Hall State Historic Site</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>https://whitehall.eku.edu</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr"/>
+      <c r="F83" s="8" t="inlineStr"/>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>US-3788</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Wickliffe Mounds State Historic Site</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/wickliffe/parks/historic/wickliffe-mounds-state-historic-site</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr"/>
+      <c r="F84" s="8" t="inlineStr"/>
+      <c r="G84" s="8" t="inlineStr"/>
+      <c r="H84" s="8" t="inlineStr"/>
+      <c r="I84" s="8" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>US-3789</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>William Whitley House State Historic Site</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>https://explorekyhistory.ky.gov/files/show/236</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr"/>
+      <c r="F85" s="8" t="inlineStr"/>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr"/>
+      <c r="I85" s="8" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>US-10102</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Pine Mountain State Trail</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>https://parks.ky.gov/whitesburg/parks/recreation/pine-mountain-state-scenic-trail</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr"/>
+      <c r="F86" s="8" t="inlineStr"/>
+      <c r="G86" s="8" t="inlineStr"/>
+      <c r="H86" s="8" t="inlineStr"/>
+      <c r="I86" s="8" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>US-11181</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Sheltowee Trace National Recreation Trail</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fs.usda.gov/wildflowers/regions/southern/SheltoweeTrace/index.shtml</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr"/>
+      <c r="F87" s="8" t="inlineStr"/>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>US-3793</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Ballard Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=224</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr"/>
+      <c r="F88" s="8" t="inlineStr"/>
+      <c r="G88" s="8" t="inlineStr"/>
+      <c r="H88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>US-3794</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Beaver Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=39</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr"/>
+      <c r="F89" s="8" t="inlineStr"/>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="8" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>US-3795</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Beechy Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/BeechyCreekWMA-ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr"/>
+      <c r="F90" s="8" t="inlineStr"/>
+      <c r="G90" s="8" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>US-3796</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Big Rivers Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9203</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>US-3797</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Boatwright Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=222</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr"/>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>US-3798</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Buck Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/BuckCreekWMA_All.pdf</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr"/>
+      <c r="F93" s="8" t="inlineStr"/>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr"/>
+      <c r="I93" s="8" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>US-3799</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Burchell-Beech Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>https://next.pota.app/park/US-3799</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr"/>
+      <c r="F94" s="8" t="inlineStr"/>
+      <c r="G94" s="8" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>US-10121</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Cane Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=38</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr"/>
+      <c r="F95" s="8" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>US-3800</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Cedar Creek Lake Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9004</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr"/>
+      <c r="F96" s="8" t="inlineStr"/>
+      <c r="G96" s="8" t="inlineStr"/>
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>US-10124</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Clay Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=155</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr"/>
+      <c r="F97" s="8" t="inlineStr"/>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>US-12974</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Clear Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=9006</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr"/>
+      <c r="F98" s="8" t="inlineStr"/>
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>US-3803</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Coil Estate Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/CoilEstateWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr"/>
+      <c r="F99" s="8" t="inlineStr"/>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>US-3804</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Cranks Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/CranksCreekWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr"/>
+      <c r="F100" s="8" t="inlineStr"/>
+      <c r="G100" s="8" t="inlineStr"/>
+      <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>US-3805</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Curtis Gates Lloyd Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=153</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr"/>
+      <c r="F101" s="8" t="inlineStr"/>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr"/>
+      <c r="I101" s="8" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>US-9756</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Decker Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9717</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr"/>
+      <c r="F102" s="8" t="inlineStr"/>
+      <c r="G102" s="8" t="inlineStr"/>
+      <c r="H102" s="8" t="inlineStr"/>
+      <c r="I102" s="8" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>US-3806</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Dennis-Gray Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=148</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr"/>
+      <c r="F103" s="8" t="inlineStr"/>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="8" t="inlineStr"/>
+      <c r="I103" s="8" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>US-4687</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Dewey Lake Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/DeweyLakeWMA-ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr"/>
+      <c r="F104" s="8" t="inlineStr"/>
+      <c r="G104" s="8" t="inlineStr"/>
+      <c r="H104" s="8" t="inlineStr"/>
+      <c r="I104" s="8" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>US-3807</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Dix River Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9032</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr"/>
+      <c r="F105" s="8" t="inlineStr"/>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr"/>
+      <c r="I105" s="8" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>US-3808</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Doug Travis Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=40</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr"/>
+      <c r="F106" s="8" t="inlineStr"/>
+      <c r="G106" s="8" t="inlineStr"/>
+      <c r="H106" s="8" t="inlineStr"/>
+      <c r="I106" s="8" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>US-3809</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Dr. James R. Rich Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=34</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr"/>
+      <c r="F107" s="8" t="inlineStr"/>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>US-3810</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Dr. Norman And Martha Adair Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>https://next.pota.app/park/US-3810</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr"/>
+      <c r="F108" s="8" t="inlineStr"/>
+      <c r="G108" s="8" t="inlineStr"/>
+      <c r="H108" s="8" t="inlineStr"/>
+      <c r="I108" s="8" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>US-3811</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Ed Mabry-Laurel Gorge Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/EdMabry-LaurelGorgeWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr"/>
+      <c r="F109" s="8" t="inlineStr"/>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="8" t="inlineStr"/>
+      <c r="I109" s="8" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>US-10128</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Ferguson Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9715</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr"/>
+      <c r="F110" s="8" t="inlineStr"/>
+      <c r="G110" s="8" t="inlineStr"/>
+      <c r="H110" s="8" t="inlineStr"/>
+      <c r="I110" s="8" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>US-1255</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>Fishtrap Lake Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=25</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr"/>
+      <c r="F111" s="8" t="inlineStr"/>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="8" t="inlineStr"/>
+      <c r="I111" s="8" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>US-3812</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>Fleming Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=154</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr"/>
+      <c r="F112" s="8" t="inlineStr"/>
+      <c r="G112" s="8" t="inlineStr"/>
+      <c r="H112" s="8" t="inlineStr"/>
+      <c r="I112" s="8" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>US-10131</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Gabbard Branch Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9713</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr"/>
+      <c r="F113" s="8" t="inlineStr"/>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="8" t="inlineStr"/>
+      <c r="I113" s="8" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>US-3813</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Griffith Woods Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>https://next.pota.app/park/US-3813</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr"/>
+      <c r="F114" s="8" t="inlineStr"/>
+      <c r="G114" s="8" t="inlineStr"/>
+      <c r="H114" s="8" t="inlineStr"/>
+      <c r="I114" s="8" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>US-10137</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Harris-Dickerson Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9709</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr"/>
+      <c r="F115" s="8" t="inlineStr"/>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="8" t="inlineStr"/>
+      <c r="I115" s="8" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>US-3814</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>Hensley-Pine Mountain Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/Hensley-PineMountainWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr"/>
+      <c r="F116" s="8" t="inlineStr"/>
+      <c r="G116" s="8" t="inlineStr"/>
+      <c r="H116" s="8" t="inlineStr"/>
+      <c r="I116" s="8" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>US-3815</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>Higginson-Henry Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=132</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr"/>
+      <c r="F117" s="8" t="inlineStr"/>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="8" t="inlineStr"/>
+      <c r="I117" s="8" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>US-11274</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Horse Mill Branch Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9721</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr"/>
+      <c r="F118" s="8" t="inlineStr"/>
+      <c r="G118" s="8" t="inlineStr"/>
+      <c r="H118" s="8" t="inlineStr"/>
+      <c r="I118" s="8" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>US-10138</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>Hoskins Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9711</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr"/>
+      <c r="F119" s="8" t="inlineStr"/>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="8" t="inlineStr"/>
+      <c r="I119" s="8" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>US-10139</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>Jefferson National Forest Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9078</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr"/>
+      <c r="F120" s="8" t="inlineStr"/>
+      <c r="G120" s="8" t="inlineStr"/>
+      <c r="H120" s="8" t="inlineStr"/>
+      <c r="I120" s="8" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>US-3816</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>John A. Kleber Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=14</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr"/>
+      <c r="F121" s="8" t="inlineStr"/>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr"/>
+      <c r="I121" s="8" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>US-3817</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>John C. Williams Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=238</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr"/>
+      <c r="F122" s="8" t="inlineStr"/>
+      <c r="G122" s="8" t="inlineStr"/>
+      <c r="H122" s="8" t="inlineStr"/>
+      <c r="I122" s="8" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>US-3818</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>Jones-Keeney Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/Jones-KeeneyWMA_All.pdf</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr"/>
+      <c r="F123" s="8" t="inlineStr"/>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="8" t="inlineStr"/>
+      <c r="I123" s="8" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>US-3819</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>Kaler Bottoms Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=21</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr"/>
+      <c r="F124" s="8" t="inlineStr"/>
+      <c r="G124" s="8" t="inlineStr"/>
+      <c r="H124" s="8" t="inlineStr"/>
+      <c r="I124" s="8" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>US-10140</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>Kentucky Lake Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=227</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr"/>
+      <c r="F125" s="8" t="inlineStr"/>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="8" t="inlineStr"/>
+      <c r="I125" s="8" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>US-10141</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>Kentucky Ridge Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=186</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr"/>
+      <c r="F126" s="8" t="inlineStr"/>
+      <c r="G126" s="8" t="inlineStr"/>
+      <c r="H126" s="8" t="inlineStr"/>
+      <c r="I126" s="8" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>US-3820</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>Kentucky River Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=169</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr"/>
+      <c r="F127" s="8" t="inlineStr"/>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="8" t="inlineStr"/>
+      <c r="I127" s="8" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>US-3821</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>L. B. Davison Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/L.B.DavisonWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr"/>
+      <c r="F128" s="8" t="inlineStr"/>
+      <c r="G128" s="8" t="inlineStr"/>
+      <c r="H128" s="8" t="inlineStr"/>
+      <c r="I128" s="8" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>US-3822</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>Lee K. Nelson Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=9011</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr"/>
+      <c r="F129" s="8" t="inlineStr"/>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="8" t="inlineStr"/>
+      <c r="I129" s="8" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>US-12079</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>Little Sextons Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/more/documents/LittleSextonsCreekWMAALL.pdf</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr"/>
+      <c r="F130" s="8" t="inlineStr"/>
+      <c r="G130" s="8" t="inlineStr"/>
+      <c r="H130" s="8" t="inlineStr"/>
+      <c r="I130" s="8" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>US-3823</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>Livingston County Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9117</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr"/>
+      <c r="F131" s="8" t="inlineStr"/>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="8" t="inlineStr"/>
+      <c r="I131" s="8" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>US-3824</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>Marion County Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/MarionCountyWMAandSF_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr"/>
+      <c r="F132" s="8" t="inlineStr"/>
+      <c r="G132" s="8" t="inlineStr"/>
+      <c r="H132" s="8" t="inlineStr"/>
+      <c r="I132" s="8" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>US-10145</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>Meadow Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9224</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr"/>
+      <c r="F133" s="8" t="inlineStr"/>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr"/>
+      <c r="I133" s="8" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>US-10146</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>Mill Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=37</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr"/>
+      <c r="F134" s="8" t="inlineStr"/>
+      <c r="G134" s="8" t="inlineStr"/>
+      <c r="H134" s="8" t="inlineStr"/>
+      <c r="I134" s="8" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>US-3825</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>Miller Welch Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=15</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr"/>
+      <c r="F135" s="8" t="inlineStr"/>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr"/>
+      <c r="I135" s="8" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>US-10148</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>Mud Camp Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=146</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr"/>
+      <c r="F136" s="8" t="inlineStr"/>
+      <c r="G136" s="8" t="inlineStr"/>
+      <c r="H136" s="8" t="inlineStr"/>
+      <c r="I136" s="8" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>US-3826</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>Mullins Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/MullinsWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr"/>
+      <c r="F137" s="8" t="inlineStr"/>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="8" t="inlineStr"/>
+      <c r="I137" s="8" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>US-3827</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>Obion Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=176</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr"/>
+      <c r="F138" s="8" t="inlineStr"/>
+      <c r="G138" s="8" t="inlineStr"/>
+      <c r="H138" s="8" t="inlineStr"/>
+      <c r="I138" s="8" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>US-10153</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>Old Trace Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9609</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="inlineStr"/>
+      <c r="F139" s="8" t="inlineStr"/>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr"/>
+      <c r="I139" s="8" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>US-10155</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>Paul Van Booven Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9105</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr"/>
+      <c r="F140" s="8" t="inlineStr"/>
+      <c r="G140" s="8" t="inlineStr"/>
+      <c r="H140" s="8" t="inlineStr"/>
+      <c r="I140" s="8" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>US-3828</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>Peabody Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=229</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr"/>
+      <c r="F141" s="8" t="inlineStr"/>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="8" t="inlineStr"/>
+      <c r="I141" s="8" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>US-10157</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>Ping-Sinking Valley Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9208</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr"/>
+      <c r="F142" s="8" t="inlineStr"/>
+      <c r="G142" s="8" t="inlineStr"/>
+      <c r="H142" s="8" t="inlineStr"/>
+      <c r="I142" s="8" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>US-10158</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>Pioneer Weapons Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=36</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr"/>
+      <c r="F143" s="8" t="inlineStr"/>
+      <c r="G143" s="8" t="inlineStr"/>
+      <c r="H143" s="8" t="inlineStr"/>
+      <c r="I143" s="8" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>US-3829</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>R. F. Tarter Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=171</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr"/>
+      <c r="F144" s="8" t="inlineStr"/>
+      <c r="G144" s="8" t="inlineStr"/>
+      <c r="H144" s="8" t="inlineStr"/>
+      <c r="I144" s="8" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>US-10159</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>Redbird Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=35</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr"/>
+      <c r="F145" s="8" t="inlineStr"/>
+      <c r="G145" s="8" t="inlineStr"/>
+      <c r="H145" s="8" t="inlineStr"/>
+      <c r="I145" s="8" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>US-10160</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>Rockcastle River Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9217</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr"/>
+      <c r="F146" s="8" t="inlineStr"/>
+      <c r="G146" s="8" t="inlineStr"/>
+      <c r="H146" s="8" t="inlineStr"/>
+      <c r="I146" s="8" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>US-10161</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>Rolling Fork Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9219</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr"/>
+      <c r="F147" s="8" t="inlineStr"/>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="8" t="inlineStr"/>
+      <c r="I147" s="8" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>US-10162</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>Ross Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9705</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr"/>
+      <c r="F148" s="8" t="inlineStr"/>
+      <c r="G148" s="8" t="inlineStr"/>
+      <c r="H148" s="8" t="inlineStr"/>
+      <c r="I148" s="8" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>US-10164</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>Shillalah Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=170</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr"/>
+      <c r="F149" s="8" t="inlineStr"/>
+      <c r="G149" s="8" t="inlineStr"/>
+      <c r="H149" s="8" t="inlineStr"/>
+      <c r="I149" s="8" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>US-10167</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>Simon Kenton Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9613</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr"/>
+      <c r="F150" s="8" t="inlineStr"/>
+      <c r="G150" s="8" t="inlineStr"/>
+      <c r="H150" s="8" t="inlineStr"/>
+      <c r="I150" s="8" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>US-3830</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>Sloughs Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=230</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr"/>
+      <c r="F151" s="8" t="inlineStr"/>
+      <c r="G151" s="8" t="inlineStr"/>
+      <c r="H151" s="8" t="inlineStr"/>
+      <c r="I151" s="8" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>US-3831</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>South Shore Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/SouthShoreWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr"/>
+      <c r="F152" s="8" t="inlineStr"/>
+      <c r="G152" s="8" t="inlineStr"/>
+      <c r="H152" s="8" t="inlineStr"/>
+      <c r="I152" s="8" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>US-10166</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>Stephens Creek Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9232</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr"/>
+      <c r="F153" s="8" t="inlineStr"/>
+      <c r="G153" s="8" t="inlineStr"/>
+      <c r="H153" s="8" t="inlineStr"/>
+      <c r="I153" s="8" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>US-3832</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>Stone Mountain Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/StoneMountainWMAandStateNaturalArea_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr"/>
+      <c r="F154" s="8" t="inlineStr"/>
+      <c r="G154" s="8" t="inlineStr"/>
+      <c r="H154" s="8" t="inlineStr"/>
+      <c r="I154" s="8" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>US-10168</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>Sunny Brook Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9707</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="inlineStr"/>
+      <c r="F155" s="8" t="inlineStr"/>
+      <c r="G155" s="8" t="inlineStr"/>
+      <c r="H155" s="8" t="inlineStr"/>
+      <c r="I155" s="8" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>US-3833</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>T. N. Sullivan Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/TN_SullivanWMA_All.pdf</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr"/>
+      <c r="F156" s="8" t="inlineStr"/>
+      <c r="G156" s="8" t="inlineStr"/>
+      <c r="H156" s="8" t="inlineStr"/>
+      <c r="I156" s="8" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>US-3834</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>Tradewater Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=128</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr"/>
+      <c r="F157" s="8" t="inlineStr"/>
+      <c r="G157" s="8" t="inlineStr"/>
+      <c r="H157" s="8" t="inlineStr"/>
+      <c r="I157" s="8" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>US-3835</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>Twin Eagle Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/TwinEagleWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr"/>
+      <c r="F158" s="8" t="inlineStr"/>
+      <c r="G158" s="8" t="inlineStr"/>
+      <c r="H158" s="8" t="inlineStr"/>
+      <c r="I158" s="8" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>US-10170</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>Twin Knobs Campground Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9116</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="inlineStr"/>
+      <c r="F159" s="8" t="inlineStr"/>
+      <c r="G159" s="8" t="inlineStr"/>
+      <c r="H159" s="8" t="inlineStr"/>
+      <c r="I159" s="8" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>US-12083</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>University of the Cumberlands Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9727</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="inlineStr"/>
+      <c r="F160" s="8" t="inlineStr"/>
+      <c r="G160" s="8" t="inlineStr"/>
+      <c r="H160" s="8" t="inlineStr"/>
+      <c r="I160" s="8" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>US-3836</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>Veterans Memorial Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9202</t>
+        </is>
+      </c>
+      <c r="E161" s="8" t="inlineStr"/>
+      <c r="F161" s="8" t="inlineStr"/>
+      <c r="G161" s="8" t="inlineStr"/>
+      <c r="H161" s="8" t="inlineStr"/>
+      <c r="I161" s="8" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>US-3837</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>West Kentucky Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=137</t>
+        </is>
+      </c>
+      <c r="E162" s="8" t="inlineStr"/>
+      <c r="F162" s="8" t="inlineStr"/>
+      <c r="G162" s="8" t="inlineStr"/>
+      <c r="H162" s="8" t="inlineStr"/>
+      <c r="I162" s="8" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>US-3838</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>Winford Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/More/Documents/WinfordWMA_ALL.pdf</t>
+        </is>
+      </c>
+      <c r="E163" s="8" t="inlineStr"/>
+      <c r="F163" s="8" t="inlineStr"/>
+      <c r="G163" s="8" t="inlineStr"/>
+      <c r="H163" s="8" t="inlineStr"/>
+      <c r="I163" s="8" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>US-3839</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>Yatesville Lake Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=23</t>
+        </is>
+      </c>
+      <c r="E164" s="8" t="inlineStr"/>
+      <c r="F164" s="8" t="inlineStr"/>
+      <c r="G164" s="8" t="inlineStr"/>
+      <c r="H164" s="8" t="inlineStr"/>
+      <c r="I164" s="8" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>US-3840</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>Yellowbank Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/public_lands_search/detail.aspx?Kdfwr_id=192</t>
+        </is>
+      </c>
+      <c r="E165" s="8" t="inlineStr"/>
+      <c r="F165" s="8" t="inlineStr"/>
+      <c r="G165" s="8" t="inlineStr"/>
+      <c r="H165" s="8" t="inlineStr"/>
+      <c r="I165" s="8" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>US-10171</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>Zilpo Campground Wildlife Management Area</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t>WMA</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/Public_Lands_Search/detail.aspx?Kdfwr_id=9094</t>
+        </is>
+      </c>
+      <c r="E166" s="8" t="inlineStr"/>
+      <c r="F166" s="8" t="inlineStr"/>
+      <c r="G166" s="8" t="inlineStr"/>
+      <c r="H166" s="8" t="inlineStr"/>
+      <c r="I166" s="8" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>US-13598</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>Beaver Lake State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=49</t>
+        </is>
+      </c>
+      <c r="E167" s="8" t="inlineStr"/>
+      <c r="F167" s="8" t="inlineStr"/>
+      <c r="G167" s="8" t="inlineStr"/>
+      <c r="H167" s="8" t="inlineStr"/>
+      <c r="I167" s="8" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>US-13607</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>Boltz State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=50</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="inlineStr"/>
+      <c r="F168" s="8" t="inlineStr"/>
+      <c r="G168" s="8" t="inlineStr"/>
+      <c r="H168" s="8" t="inlineStr"/>
+      <c r="I168" s="8" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>US-13606</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>Bullock Pen State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=51</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr"/>
+      <c r="F169" s="8" t="inlineStr"/>
+      <c r="G169" s="8" t="inlineStr"/>
+      <c r="H169" s="8" t="inlineStr"/>
+      <c r="I169" s="8" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>US-13600</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>Carpenters Lake State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=39</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr"/>
+      <c r="F170" s="8" t="inlineStr"/>
+      <c r="G170" s="8" t="inlineStr"/>
+      <c r="H170" s="8" t="inlineStr"/>
+      <c r="I170" s="8" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>US-3801</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>Clifty Wilderness Area</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>River / Wilderness</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fs.usda.gov/recarea/dbnf/recarea/?recid=39460</t>
+        </is>
+      </c>
+      <c r="E171" s="8" t="inlineStr"/>
+      <c r="F171" s="8" t="inlineStr"/>
+      <c r="G171" s="8" t="inlineStr"/>
+      <c r="H171" s="8" t="inlineStr"/>
+      <c r="I171" s="8" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>US-3802</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>Clyde E Buckley Sanctuary</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>Sanctuary</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>https://bggreensource.org/buckley/</t>
+        </is>
+      </c>
+      <c r="E172" s="8" t="inlineStr"/>
+      <c r="F172" s="8" t="inlineStr"/>
+      <c r="G172" s="8" t="inlineStr"/>
+      <c r="H172" s="8" t="inlineStr"/>
+      <c r="I172" s="8" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>US-4484</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>Daniel Boone National Forest</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>National Forest</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fs.usda.gov/dbnf/</t>
+        </is>
+      </c>
+      <c r="E173" s="8" t="inlineStr"/>
+      <c r="F173" s="8" t="inlineStr"/>
+      <c r="G173" s="8" t="inlineStr"/>
+      <c r="H173" s="8" t="inlineStr"/>
+      <c r="I173" s="8" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>US-4526</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>George Washington &amp; Jefferson National Forest</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>National Forest</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fs.usda.gov/gwj</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr"/>
+      <c r="F174" s="8" t="inlineStr"/>
+      <c r="G174" s="8" t="inlineStr"/>
+      <c r="H174" s="8" t="inlineStr"/>
+      <c r="I174" s="8" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>US-13601</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>Guist Creek Lake State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=56</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr"/>
+      <c r="F175" s="8" t="inlineStr"/>
+      <c r="G175" s="8" t="inlineStr"/>
+      <c r="H175" s="8" t="inlineStr"/>
+      <c r="I175" s="8" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t>US-10173</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>Kentucky Horse Park</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>State Facility</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kyhorsepark.com/</t>
+        </is>
+      </c>
+      <c r="E176" s="8" t="inlineStr"/>
+      <c r="F176" s="8" t="inlineStr"/>
+      <c r="G176" s="8" t="inlineStr"/>
+      <c r="H176" s="8" t="inlineStr"/>
+      <c r="I176" s="8" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>US-13599</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>Kingfisher Lakes State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>State Fishing Lake</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>https://app.fw.ky.gov/fisheries/waterbodydetail.aspx?wid=40</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr"/>
+      <c r="F177" s="8" t="inlineStr"/>
+      <c r="G177" s="8" t="inlineStr"/>
+      <c r="H177" s="8" t="inlineStr"/>
+      <c r="I177" s="8" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>US-3792</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>Land Between the Lakes National Recreation Area</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>National Recreation Area</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>https://landbetweenthelakes.us/</t>
+        </is>
+      </c>
+      <c r="E178" s="8" t="inlineStr"/>
+      <c r="F178" s="8" t="inlineStr"/>
+      <c r="G178" s="8" t="inlineStr"/>
+      <c r="H178" s="8" t="inlineStr"/>
+      <c r="I178" s="8" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>US-8144</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>Otter Creek State Recreation Area</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>Recreation Area</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>https://fw.ky.gov/Pages/Otter-Creek-Outdoor-Recreation-Area.aspx</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="inlineStr"/>
+      <c r="F179" s="8" t="inlineStr"/>
+      <c r="G179" s="8" t="inlineStr"/>
+      <c r="H179" s="8" t="inlineStr"/>
+      <c r="I179" s="8" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>US-10103</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>The Cumberland River Wilderness Area</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>River / Wilderness</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Nature-Preserves/Locations/Pages/Cumberland-River-Wild-River.aspx</t>
+        </is>
+      </c>
+      <c r="E180" s="8" t="inlineStr"/>
+      <c r="F180" s="8" t="inlineStr"/>
+      <c r="G180" s="8" t="inlineStr"/>
+      <c r="H180" s="8" t="inlineStr"/>
+      <c r="I180" s="8" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>US-10099</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>Wolf Creek National Fish Hatchery</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>Fish Hatchery</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fws.gov/fish-hatchery/wolf-creek/map</t>
+        </is>
+      </c>
+      <c r="E181" s="8" t="inlineStr"/>
+      <c r="F181" s="8" t="inlineStr"/>
+      <c r="G181" s="8" t="inlineStr"/>
+      <c r="H181" s="8" t="inlineStr"/>
+      <c r="I181" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
